--- a/docs/Files/ODYM_Tutorial6_FabricationYieldLoss_V1.0_EVLIB.xlsx
+++ b/docs/Files/ODYM_Tutorial6_FabricationYieldLoss_V1.0_EVLIB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5561678A-D2B3-4391-A1C1-0272A81C874B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB79D1C6-E9AE-4497-B560-84B8F8D69479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="110">
   <si>
     <t>Format_Version</t>
   </si>
@@ -1205,6 +1205,9 @@
       <c r="D2" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="E2">
+        <v>0.31</v>
+      </c>
       <c r="F2">
         <v>1</v>
       </c>
@@ -1228,6 +1231,9 @@
       <c r="D3" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="E3">
+        <v>0.2</v>
+      </c>
       <c r="F3">
         <v>1</v>
       </c>
@@ -1251,6 +1257,9 @@
       <c r="D4" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="E4">
+        <v>0.06</v>
+      </c>
       <c r="F4">
         <v>1</v>
       </c>
@@ -1274,6 +1283,9 @@
       <c r="D5" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="E5">
+        <v>0.23</v>
+      </c>
       <c r="F5">
         <v>1</v>
       </c>
@@ -1297,6 +1309,9 @@
       <c r="D6" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="E6">
+        <v>0.155</v>
+      </c>
       <c r="F6">
         <v>1</v>
       </c>
@@ -1320,6 +1335,9 @@
       <c r="D7" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="E7">
+        <v>0.1</v>
+      </c>
       <c r="F7">
         <v>1</v>
       </c>
@@ -1343,6 +1361,9 @@
       <c r="D8" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="E8">
+        <v>0.03</v>
+      </c>
       <c r="F8">
         <v>1</v>
       </c>
@@ -1366,6 +1387,9 @@
       <c r="D9" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="E9">
+        <v>0.115</v>
+      </c>
       <c r="F9">
         <v>1</v>
       </c>
@@ -1389,6 +1413,9 @@
       <c r="D10" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="E10">
+        <v>3.3749999999999697E-2</v>
+      </c>
       <c r="F10">
         <v>1</v>
       </c>
@@ -1412,6 +1439,9 @@
       <c r="D11" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="E11">
+        <v>0.31</v>
+      </c>
       <c r="F11">
         <v>1</v>
       </c>
@@ -1435,6 +1465,9 @@
       <c r="D12" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="E12">
+        <v>0.2</v>
+      </c>
       <c r="F12">
         <v>1</v>
       </c>
@@ -1458,6 +1491,9 @@
       <c r="D13" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="E13">
+        <v>0.06</v>
+      </c>
       <c r="F13">
         <v>1</v>
       </c>
@@ -1481,6 +1517,9 @@
       <c r="D14" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="E14">
+        <v>0.23</v>
+      </c>
       <c r="F14">
         <v>1</v>
       </c>
@@ -1504,6 +1543,9 @@
       <c r="D15" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="E15">
+        <v>0.155</v>
+      </c>
       <c r="F15">
         <v>1</v>
       </c>
@@ -1527,6 +1569,9 @@
       <c r="D16" s="1" t="s">
         <v>106</v>
       </c>
+      <c r="E16">
+        <v>0.1</v>
+      </c>
       <c r="F16">
         <v>1</v>
       </c>
@@ -1550,6 +1595,9 @@
       <c r="D17" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="E17">
+        <v>0.03</v>
+      </c>
       <c r="F17">
         <v>1</v>
       </c>
@@ -1558,6 +1606,11 @@
       </c>
       <c r="H17" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E22" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.35">
